--- a/Assets/GameSample/Forms/Excels/Story/Event/GameCmdData_CmdData.xlsx
+++ b/Assets/GameSample/Forms/Excels/Story/Event/GameCmdData_CmdData.xlsx
@@ -5669,11 +5669,15 @@
       <x:c r="B104" s="2" t="s">
         <x:v>489</x:v>
       </x:c>
-      <x:c r="C104" s="2" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D104" s="2" t="s">
-        <x:v>27</x:v>
+      <x:c r="C104" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
+      </x:c>
+      <x:c r="D104" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
       </x:c>
       <x:c r="E104" s="2" t="s">
         <x:v>491</x:v>
@@ -5684,8 +5688,10 @@
       <x:c r="G104" s="2" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="H104" s="2" t="s">
-        <x:v>493</x:v>
+      <x:c r="H104" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>IsMissionAdded("$m$$m$")</t>
+        </is>
       </x:c>
       <x:c r="I104" s="2">
         <x:v>10015</x:v>
@@ -5702,11 +5708,15 @@
       <x:c r="B105" s="2" t="s">
         <x:v>495</x:v>
       </x:c>
-      <x:c r="C105" s="2" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D105" s="2" t="s">
-        <x:v>27</x:v>
+      <x:c r="C105" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
+      </x:c>
+      <x:c r="D105" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
       </x:c>
       <x:c r="E105" s="2" t="s">
         <x:v>496</x:v>
@@ -5717,8 +5727,10 @@
       <x:c r="G105" s="2" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="H105" s="2" t="s">
-        <x:v>498</x:v>
+      <x:c r="H105" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>HasMissionDone("$m$$m$")</t>
+        </is>
       </x:c>
       <x:c r="I105" s="2">
         <x:v>10015</x:v>
@@ -5735,11 +5747,15 @@
       <x:c r="B106" s="2" t="s">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="C106" s="2" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D106" s="2" t="s">
-        <x:v>27</x:v>
+      <x:c r="C106" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
+      </x:c>
+      <x:c r="D106" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
       </x:c>
       <x:c r="E106" s="2"/>
       <x:c r="F106" s="2" t="s">
@@ -5748,8 +5764,10 @@
       <x:c r="G106" s="2" t="s">
         <x:v>501</x:v>
       </x:c>
-      <x:c r="H106" s="2" t="s">
-        <x:v>502</x:v>
+      <x:c r="H106" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>AddMission("$m$$m$");</t>
+        </is>
       </x:c>
       <x:c r="I106" s="2">
         <x:v>10015</x:v>
@@ -5766,11 +5784,15 @@
       <x:c r="B107" s="2" t="s">
         <x:v>504</x:v>
       </x:c>
-      <x:c r="C107" s="2" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="D107" s="2" t="s">
-        <x:v>27</x:v>
+      <x:c r="C107" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
+      </x:c>
+      <x:c r="D107" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>mission</t>
+        </is>
       </x:c>
       <x:c r="E107" s="2"/>
       <x:c r="F107" s="2" t="s">
@@ -5779,8 +5801,10 @@
       <x:c r="G107" s="2" t="s">
         <x:v>505</x:v>
       </x:c>
-      <x:c r="H107" s="2" t="s">
-        <x:v>506</x:v>
+      <x:c r="H107" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>DoneMission("$m$$m$");</t>
+        </is>
       </x:c>
       <x:c r="I107" s="2">
         <x:v>10015</x:v>
@@ -5947,6 +5971,51 @@
       </x:c>
       <x:c r="K112" s="2"/>
     </x:row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>100108</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>mission</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>mission</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>"$m$$m$"</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Rpg</t>
+        </is>
+      </c>
+      <c r="K113" s="2"/>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
